--- a/docs/customer-frontend-qa-checklist-dev-smoke-env.xlsx
+++ b/docs/customer-frontend-qa-checklist-dev-smoke-env.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ayanc\OneDrive\Desktop\cabbo-frontends\cabbo-customer-frontend\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B39AC99-5995-4155-9A4D-D9F53DDCBE6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FAC6143-92D4-4907-9372-C4E652115AE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="168">
   <si>
     <t>Cabbo Customer Frontend QA Checklist (Dev Smoke Env)</t>
   </si>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="B9">
         <f>COUNTIF(Checklist!H2:H200,"Pass")</f>
-        <v>16</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="B12">
         <f>COUNTIF(Checklist!H2:H200,"")</f>
-        <v>183</v>
+        <v>172</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
@@ -1945,7 +1945,9 @@
       <c r="G18" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="H18" s="9"/>
+      <c r="H18" s="7" t="s">
+        <v>165</v>
+      </c>
       <c r="I18" s="6" t="s">
         <v>166</v>
       </c>
@@ -1979,7 +1981,9 @@
       <c r="G19" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="H19" s="9"/>
+      <c r="H19" s="7" t="s">
+        <v>165</v>
+      </c>
       <c r="I19" s="6" t="s">
         <v>166</v>
       </c>
@@ -2013,7 +2017,9 @@
       <c r="G20" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="H20" s="9"/>
+      <c r="H20" s="7" t="s">
+        <v>165</v>
+      </c>
       <c r="I20" s="6" t="s">
         <v>166</v>
       </c>
@@ -2047,7 +2053,9 @@
       <c r="G21" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="H21" s="9"/>
+      <c r="H21" s="7" t="s">
+        <v>165</v>
+      </c>
       <c r="I21" s="6" t="s">
         <v>166</v>
       </c>
@@ -2081,7 +2089,9 @@
       <c r="G22" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="H22" s="9"/>
+      <c r="H22" s="7" t="s">
+        <v>165</v>
+      </c>
       <c r="I22" s="6" t="s">
         <v>166</v>
       </c>
@@ -2149,7 +2159,9 @@
       <c r="G24" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="H24" s="9"/>
+      <c r="H24" s="7" t="s">
+        <v>165</v>
+      </c>
       <c r="I24" s="6" t="s">
         <v>166</v>
       </c>
@@ -2183,7 +2195,9 @@
       <c r="G25" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="H25" s="9"/>
+      <c r="H25" s="7" t="s">
+        <v>165</v>
+      </c>
       <c r="I25" s="6" t="s">
         <v>166</v>
       </c>
@@ -2217,7 +2231,9 @@
       <c r="G26" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="H26" s="9"/>
+      <c r="H26" s="7" t="s">
+        <v>165</v>
+      </c>
       <c r="I26" s="6" t="s">
         <v>166</v>
       </c>
@@ -2251,7 +2267,9 @@
       <c r="G27" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="H27" s="9"/>
+      <c r="H27" s="7" t="s">
+        <v>165</v>
+      </c>
       <c r="I27" s="6" t="s">
         <v>166</v>
       </c>
@@ -2319,7 +2337,9 @@
       <c r="G29" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="H29" s="9"/>
+      <c r="H29" s="7" t="s">
+        <v>165</v>
+      </c>
       <c r="I29" s="6" t="s">
         <v>166</v>
       </c>
@@ -2353,7 +2373,9 @@
       <c r="G30" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="H30" s="9"/>
+      <c r="H30" s="7" t="s">
+        <v>165</v>
+      </c>
       <c r="I30" s="6" t="s">
         <v>166</v>
       </c>

--- a/docs/customer-frontend-qa-checklist-dev-smoke-env.xlsx
+++ b/docs/customer-frontend-qa-checklist-dev-smoke-env.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ayanc\OneDrive\Desktop\cabbo-frontends\cabbo-customer-frontend\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FAC6143-92D4-4907-9372-C4E652115AE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D08D739-210C-443B-BB75-253497ACB923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -18,15 +18,12 @@
     <sheet name="Checklist" sheetId="3" r:id="rId3"/>
     <sheet name="Defects Log" sheetId="4" r:id="rId4"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId5"/>
-  </externalReferences>
   <calcPr calcId="191029" forceFullCalc="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="168">
   <si>
     <t>Cabbo Customer Frontend QA Checklist (Dev Smoke Env)</t>
   </si>
@@ -686,7 +683,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -714,9 +711,6 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -741,19 +735,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Log"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1133,7 +1114,7 @@
       </c>
       <c r="B9">
         <f>COUNTIF(Checklist!H2:H200,"Pass")</f>
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -1157,22 +1138,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>18</v>
       </c>
       <c r="B12">
         <f>COUNTIF(Checklist!H2:H200,"")</f>
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>19</v>
       </c>
-      <c r="B13" t="e">
-        <f>COUNTIFS(Defects [1]Log!E2:E100,"P0",Defects [1]Log!F2:F100,"&lt;&gt;Closed")</f>
-        <v>#NAME?</v>
+      <c r="B13">
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
@@ -1348,7 +1328,7 @@
       </c>
     </row>
     <row r="2" spans="1:14" ht="29" x14ac:dyDescent="0.35">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>52</v>
       </c>
       <c r="B2" s="6" t="s">
@@ -1384,7 +1364,7 @@
       <c r="N2" s="3"/>
     </row>
     <row r="3" spans="1:14" ht="29" x14ac:dyDescent="0.35">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="9" t="s">
         <v>52</v>
       </c>
       <c r="B3" s="6" t="s">
@@ -1420,7 +1400,7 @@
       <c r="N3" s="3"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="9" t="s">
         <v>52</v>
       </c>
       <c r="B4" s="6" t="s">
@@ -1456,7 +1436,7 @@
       <c r="N4" s="3"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="9" t="s">
         <v>52</v>
       </c>
       <c r="B5" s="6" t="s">
@@ -1492,7 +1472,7 @@
       <c r="N5" s="3"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="9" t="s">
         <v>52</v>
       </c>
       <c r="B6" s="6" t="s">
@@ -1528,7 +1508,7 @@
       <c r="N6" s="3"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="9" t="s">
         <v>52</v>
       </c>
       <c r="B7" s="6" t="s">
@@ -1564,7 +1544,7 @@
       <c r="N7" s="3"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="9" t="s">
         <v>52</v>
       </c>
       <c r="B8" s="6" t="s">
@@ -1600,7 +1580,7 @@
       <c r="N8" s="3"/>
     </row>
     <row r="9" spans="1:14" ht="29" x14ac:dyDescent="0.35">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="10" t="s">
         <v>81</v>
       </c>
       <c r="B9" s="6" t="s">
@@ -1612,7 +1592,7 @@
       <c r="D9" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="11" t="s">
         <v>75</v>
       </c>
       <c r="F9" s="6" t="s">
@@ -1636,7 +1616,7 @@
       <c r="N9" s="3"/>
     </row>
     <row r="10" spans="1:14" ht="29" x14ac:dyDescent="0.35">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="9" t="s">
         <v>52</v>
       </c>
       <c r="B10" s="6" t="s">
@@ -1672,7 +1652,7 @@
       <c r="N10" s="3"/>
     </row>
     <row r="11" spans="1:14" ht="29" x14ac:dyDescent="0.35">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="9" t="s">
         <v>52</v>
       </c>
       <c r="B11" s="6" t="s">
@@ -1684,10 +1664,10 @@
       <c r="D11" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="E11" s="12" t="s">
+      <c r="E11" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="F11" s="12" t="s">
+      <c r="F11" s="11" t="s">
         <v>167</v>
       </c>
       <c r="G11" s="6" t="s">
@@ -1708,7 +1688,7 @@
       <c r="N11" s="3"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="9" t="s">
         <v>52</v>
       </c>
       <c r="B12" s="6" t="s">
@@ -1744,7 +1724,7 @@
       <c r="N12" s="3"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="9" t="s">
         <v>52</v>
       </c>
       <c r="B13" s="6" t="s">
@@ -1780,7 +1760,7 @@
       <c r="N13" s="3"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="9" t="s">
         <v>52</v>
       </c>
       <c r="B14" s="6" t="s">
@@ -1816,7 +1796,7 @@
       <c r="N14" s="3"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="9" t="s">
         <v>52</v>
       </c>
       <c r="B15" s="6" t="s">
@@ -1852,7 +1832,7 @@
       <c r="N15" s="3"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="9" t="s">
         <v>52</v>
       </c>
       <c r="B16" s="6" t="s">
@@ -1888,7 +1868,7 @@
       <c r="N16" s="3"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="9" t="s">
         <v>52</v>
       </c>
       <c r="B17" s="6" t="s">
@@ -1924,7 +1904,7 @@
       <c r="N17" s="3"/>
     </row>
     <row r="18" spans="1:14" ht="29" x14ac:dyDescent="0.35">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="9" t="s">
         <v>52</v>
       </c>
       <c r="B18" s="6" t="s">
@@ -1960,7 +1940,7 @@
       <c r="N18" s="3"/>
     </row>
     <row r="19" spans="1:14" ht="29" x14ac:dyDescent="0.35">
-      <c r="A19" s="10" t="s">
+      <c r="A19" s="9" t="s">
         <v>52</v>
       </c>
       <c r="B19" s="6" t="s">
@@ -1996,7 +1976,7 @@
       <c r="N19" s="3"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A20" s="10" t="s">
+      <c r="A20" s="9" t="s">
         <v>52</v>
       </c>
       <c r="B20" s="6" t="s">
@@ -2032,7 +2012,7 @@
       <c r="N20" s="3"/>
     </row>
     <row r="21" spans="1:14" ht="29" x14ac:dyDescent="0.35">
-      <c r="A21" s="10" t="s">
+      <c r="A21" s="9" t="s">
         <v>52</v>
       </c>
       <c r="B21" s="6" t="s">
@@ -2068,7 +2048,7 @@
       <c r="N21" s="3"/>
     </row>
     <row r="22" spans="1:14" ht="29" x14ac:dyDescent="0.35">
-      <c r="A22" s="11" t="s">
+      <c r="A22" s="10" t="s">
         <v>81</v>
       </c>
       <c r="B22" s="6" t="s">
@@ -2104,7 +2084,7 @@
       <c r="N22" s="3"/>
     </row>
     <row r="23" spans="1:14" ht="29" x14ac:dyDescent="0.35">
-      <c r="A23" s="11" t="s">
+      <c r="A23" s="10" t="s">
         <v>81</v>
       </c>
       <c r="B23" s="6" t="s">
@@ -2125,7 +2105,9 @@
       <c r="G23" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="H23" s="9"/>
+      <c r="H23" s="7" t="s">
+        <v>165</v>
+      </c>
       <c r="I23" s="6" t="s">
         <v>166</v>
       </c>
@@ -2138,7 +2120,7 @@
       <c r="N23" s="3"/>
     </row>
     <row r="24" spans="1:14" ht="29" x14ac:dyDescent="0.35">
-      <c r="A24" s="11" t="s">
+      <c r="A24" s="10" t="s">
         <v>81</v>
       </c>
       <c r="B24" s="6" t="s">
@@ -2174,7 +2156,7 @@
       <c r="N24" s="3"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A25" s="11" t="s">
+      <c r="A25" s="10" t="s">
         <v>81</v>
       </c>
       <c r="B25" s="6" t="s">
@@ -2210,7 +2192,7 @@
       <c r="N25" s="3"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A26" s="11" t="s">
+      <c r="A26" s="10" t="s">
         <v>81</v>
       </c>
       <c r="B26" s="6" t="s">
@@ -2246,7 +2228,7 @@
       <c r="N26" s="3"/>
     </row>
     <row r="27" spans="1:14" ht="29" x14ac:dyDescent="0.35">
-      <c r="A27" s="10" t="s">
+      <c r="A27" s="9" t="s">
         <v>52</v>
       </c>
       <c r="B27" s="6" t="s">
@@ -2282,7 +2264,7 @@
       <c r="N27" s="3"/>
     </row>
     <row r="28" spans="1:14" ht="29" x14ac:dyDescent="0.35">
-      <c r="A28" s="11" t="s">
+      <c r="A28" s="10" t="s">
         <v>81</v>
       </c>
       <c r="B28" s="6" t="s">
@@ -2303,7 +2285,9 @@
       <c r="G28" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="H28" s="9"/>
+      <c r="H28" s="7" t="s">
+        <v>165</v>
+      </c>
       <c r="I28" s="6" t="s">
         <v>166</v>
       </c>
@@ -2316,7 +2300,7 @@
       <c r="N28" s="3"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A29" s="11" t="s">
+      <c r="A29" s="10" t="s">
         <v>81</v>
       </c>
       <c r="B29" s="6" t="s">
@@ -2352,7 +2336,7 @@
       <c r="N29" s="3"/>
     </row>
     <row r="30" spans="1:14" ht="29" x14ac:dyDescent="0.35">
-      <c r="A30" s="11" t="s">
+      <c r="A30" s="10" t="s">
         <v>81</v>
       </c>
       <c r="B30" s="6" t="s">
